--- a/5 Advance Excel in Data Analysis/16 Data Validation & Dropdown in Excel.xlsx
+++ b/5 Advance Excel in Data Analysis/16 Data Validation & Dropdown in Excel.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amand\Desktop\Data Analysis\5 Advance Excel in Data Analysis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B49F8B1-F32B-4949-9C18-4A32620E0BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,10 +24,62 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+  <si>
+    <t>Students</t>
+  </si>
+  <si>
+    <t>Marks in Maths</t>
+  </si>
+  <si>
+    <t>Marks in Physics</t>
+  </si>
+  <si>
+    <t>Marks in Chemistry</t>
+  </si>
+  <si>
+    <t>Good Behaviour</t>
+  </si>
+  <si>
+    <t>Shubham</t>
+  </si>
+  <si>
+    <t>Aman</t>
+  </si>
+  <si>
+    <t>Sanya</t>
+  </si>
+  <si>
+    <t>Divya</t>
+  </si>
+  <si>
+    <t>Ram</t>
+  </si>
+  <si>
+    <t>Shayam</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -37,7 +95,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -45,17 +103,351 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="10">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -66,6 +458,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DB88153F-49DA-4084-8BF4-C928B396472B}" name="Table1" displayName="Table1" ref="A1:E7" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{C17424E3-438E-45F1-B6EA-3271B514878E}" name="Students" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{8580B4E1-2E3E-416B-B338-AB4B38BD90E4}" name="Marks in Maths" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{EC77BB58-CD3A-4138-98CA-CEE24B6F519A}" name="Marks in Physics" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{7D885DF3-1678-4D8D-BFFC-1B6343899F0D}" name="Marks in Chemistry" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{5DD23E0A-FC3F-43B4-ADE4-4D959493926B}" name="Good Behaviour" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +735,149 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="9.86328125" customWidth="1"/>
+    <col min="2" max="2" width="15.19921875" customWidth="1"/>
+    <col min="3" max="3" width="15.9296875" customWidth="1"/>
+    <col min="4" max="4" width="18.265625" customWidth="1"/>
+    <col min="5" max="5" width="15.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5">
+        <v>34</v>
+      </c>
+      <c r="C2" s="5">
+        <v>55</v>
+      </c>
+      <c r="D2" s="5">
+        <v>56</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5">
+        <v>55</v>
+      </c>
+      <c r="C3" s="5">
+        <v>56</v>
+      </c>
+      <c r="D3" s="5">
+        <v>78</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5">
+        <v>34</v>
+      </c>
+      <c r="C4" s="5">
+        <v>67</v>
+      </c>
+      <c r="D4" s="5">
+        <v>55</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="5">
+        <v>87</v>
+      </c>
+      <c r="C5" s="5">
+        <v>78</v>
+      </c>
+      <c r="D5" s="5">
+        <v>54</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="5">
+        <v>90</v>
+      </c>
+      <c r="C6" s="5">
+        <v>89</v>
+      </c>
+      <c r="D6" s="5">
+        <v>56</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="8">
+        <v>34</v>
+      </c>
+      <c r="C7" s="8">
+        <v>55</v>
+      </c>
+      <c r="D7" s="8">
+        <v>56</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E7" xr:uid="{34C07AED-4DF1-4AA9-97C1-B963CB7DBDD5}">
+      <formula1>"Yes, No, Maybe"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:D7" xr:uid="{0E5164F0-1B93-4968-BFD6-FDD7FC277B5F}">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>